--- a/Main Input Files/LP MSF mapping.xlsx
+++ b/Main Input Files/LP MSF mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://riotinto-my.sharepoint.com/personal/oliver_lartigue_riotinto_com/Documents/Documents/31. Tool for LP SL computation/Main Input Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{9196A4BE-9526-4D37-A78A-11F0745B5C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C37CD769-5BB4-4459-AFB2-F297CC86E443}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{9196A4BE-9526-4D37-A78A-11F0745B5C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79351E54-9BB8-4F5A-9C4D-D57A5CAAAE74}"/>
   <bookViews>
-    <workbookView xWindow="1872" yWindow="4032" windowWidth="17280" windowHeight="8880" xr2:uid="{26E0F985-04E8-41B0-A2C7-BBAD4DDF7EE7}"/>
+    <workbookView xWindow="-12795" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{26E0F985-04E8-41B0-A2C7-BBAD4DDF7EE7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="198">
   <si>
     <t>assetGroupingPK</t>
   </si>
@@ -618,10 +618,25 @@
     <t>YANPLT02BYPASS</t>
   </si>
   <si>
-    <t>YA Plant 3</t>
-  </si>
-  <si>
-    <t>Yandi Loop Plant</t>
+    <t>BM4SC401</t>
+  </si>
+  <si>
+    <t>BM4SC402</t>
+  </si>
+  <si>
+    <t>BM4SC403</t>
+  </si>
+  <si>
+    <t>BM4SC404</t>
+  </si>
+  <si>
+    <t>BM4SC405</t>
+  </si>
+  <si>
+    <t>BM4SC406</t>
+  </si>
+  <si>
+    <t>MTPCV85C</t>
   </si>
 </sst>
 </file>
@@ -1237,7 +1252,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF7ADCA9-084A-4F6A-B07C-E2482E2DBBC6}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F179"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1264,7 +1278,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1502</v>
       </c>
@@ -1284,7 +1298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1502</v>
       </c>
@@ -1304,7 +1318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1324,7 +1338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1344,7 +1358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1364,7 +1378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3</v>
       </c>
@@ -1384,7 +1398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1618</v>
       </c>
@@ -1404,7 +1418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1618</v>
       </c>
@@ -1424,7 +1438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1441,10 +1455,10 @@
         <v>13</v>
       </c>
       <c r="F10">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
@@ -1461,10 +1475,10 @@
         <v>16</v>
       </c>
       <c r="F11">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -1484,7 +1498,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -1504,172 +1518,172 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>191</v>
+      </c>
+      <c r="F14">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>192</v>
+      </c>
+      <c r="F15">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>193</v>
+      </c>
+      <c r="F16">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
+        <v>194</v>
+      </c>
+      <c r="F17">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>195</v>
+      </c>
+      <c r="F18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>196</v>
+      </c>
+      <c r="F19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>21</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B20" t="s">
         <v>21</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>21</v>
-      </c>
-      <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>23</v>
-      </c>
-      <c r="B18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>88</v>
-      </c>
-      <c r="B19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>31</v>
-      </c>
-      <c r="B20" t="s">
-        <v>30</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
         <v>22</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>
@@ -1678,18 +1692,18 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
@@ -1698,18 +1712,18 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F23">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
         <v>22</v>
@@ -1718,18 +1732,18 @@
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F24">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
         <v>22</v>
@@ -1738,53 +1752,53 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>35</v>
-      </c>
-      <c r="F25">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
         <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F26">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
         <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25</v>
       </c>
@@ -1798,173 +1812,173 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F28">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
         <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
         <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E30" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
+        <v>35</v>
+      </c>
+      <c r="F31">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>30</v>
+      </c>
+      <c r="B35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>30</v>
+      </c>
+      <c r="B36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" t="s">
         <v>40</v>
       </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>9</v>
-      </c>
-      <c r="B31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" t="s">
-        <v>43</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>9</v>
-      </c>
-      <c r="B32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>9</v>
-      </c>
-      <c r="B33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" t="s">
-        <v>45</v>
-      </c>
-      <c r="F33">
-        <v>9.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>9</v>
-      </c>
-      <c r="B34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" t="s">
-        <v>46</v>
-      </c>
-      <c r="F34">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>9</v>
-      </c>
-      <c r="B35" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" t="s">
-        <v>47</v>
-      </c>
-      <c r="F35">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>9</v>
-      </c>
-      <c r="B36" t="s">
-        <v>41</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" t="s">
-        <v>48</v>
-      </c>
       <c r="F36">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>9</v>
       </c>
@@ -1978,13 +1992,13 @@
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F37">
-        <v>9.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>9</v>
       </c>
@@ -1998,13 +2012,13 @@
         <v>20</v>
       </c>
       <c r="E38" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F38">
-        <v>9.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>9</v>
       </c>
@@ -2018,138 +2032,138 @@
         <v>20</v>
       </c>
       <c r="E39" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F39">
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
+        <v>9</v>
+      </c>
+      <c r="B40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" t="s">
+        <v>46</v>
+      </c>
+      <c r="F40">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" t="s">
+        <v>47</v>
+      </c>
+      <c r="F41">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" t="s">
+        <v>48</v>
+      </c>
+      <c r="F42">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>9</v>
+      </c>
+      <c r="B43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>9</v>
+      </c>
+      <c r="B44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" t="s">
+        <v>50</v>
+      </c>
+      <c r="F44">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>9</v>
+      </c>
+      <c r="B45" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46">
         <v>1651</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B46" t="s">
         <v>52</v>
-      </c>
-      <c r="C40" t="s">
-        <v>53</v>
-      </c>
-      <c r="D40" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>87</v>
-      </c>
-      <c r="B41" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" t="s">
-        <v>53</v>
-      </c>
-      <c r="D41" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" t="s">
-        <v>55</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>46</v>
-      </c>
-      <c r="B42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C42" t="s">
-        <v>53</v>
-      </c>
-      <c r="D42" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" t="s">
-        <v>55</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>46</v>
-      </c>
-      <c r="B43" t="s">
-        <v>56</v>
-      </c>
-      <c r="C43" t="s">
-        <v>53</v>
-      </c>
-      <c r="D43" t="s">
-        <v>20</v>
-      </c>
-      <c r="E43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F43">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>46</v>
-      </c>
-      <c r="B44" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" t="s">
-        <v>53</v>
-      </c>
-      <c r="D44" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" t="s">
-        <v>58</v>
-      </c>
-      <c r="F44">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>1644</v>
-      </c>
-      <c r="B45" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>60</v>
       </c>
       <c r="C46" t="s">
         <v>53</v>
@@ -2158,278 +2172,278 @@
         <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>61</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="F46" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D47" t="s">
         <v>8</v>
       </c>
       <c r="E47" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E48" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D49" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E49" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D50" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E50" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>48</v>
+        <v>1644</v>
       </c>
       <c r="B51" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D51" t="s">
         <v>20</v>
       </c>
       <c r="E51" t="s">
-        <v>64</v>
-      </c>
-      <c r="F51">
-        <v>0.2</v>
+        <v>7</v>
+      </c>
+      <c r="F51" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D52" t="s">
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F52">
-        <v>0.28999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C53" t="s">
         <v>63</v>
       </c>
       <c r="D53" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E53" t="s">
+        <v>64</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>49</v>
+      </c>
+      <c r="B54" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" t="s">
+        <v>63</v>
+      </c>
+      <c r="D54" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" t="s">
         <v>65</v>
       </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A54">
+      <c r="F54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>50</v>
+      </c>
+      <c r="B55" t="s">
+        <v>66</v>
+      </c>
+      <c r="C55" t="s">
+        <v>63</v>
+      </c>
+      <c r="D55" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" t="s">
+        <v>67</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>50</v>
+      </c>
+      <c r="B56" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" t="s">
+        <v>65</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>48</v>
+      </c>
+      <c r="B57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" t="s">
+        <v>63</v>
+      </c>
+      <c r="D57" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" t="s">
+        <v>64</v>
+      </c>
+      <c r="F57">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>48</v>
+      </c>
+      <c r="B58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" t="s">
+        <v>63</v>
+      </c>
+      <c r="D58" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" t="s">
+        <v>67</v>
+      </c>
+      <c r="F58">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>48</v>
+      </c>
+      <c r="B59" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" t="s">
+        <v>65</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60">
         <v>1653</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B60" t="s">
         <v>69</v>
-      </c>
-      <c r="C54" t="s">
-        <v>70</v>
-      </c>
-      <c r="D54" t="s">
-        <v>20</v>
-      </c>
-      <c r="E54" t="s">
-        <v>71</v>
-      </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>55</v>
-      </c>
-      <c r="B55" t="s">
-        <v>72</v>
-      </c>
-      <c r="C55" t="s">
-        <v>70</v>
-      </c>
-      <c r="D55" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" t="s">
-        <v>73</v>
-      </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="s">
-        <v>72</v>
-      </c>
-      <c r="C56" t="s">
-        <v>70</v>
-      </c>
-      <c r="D56" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" t="s">
-        <v>74</v>
-      </c>
-      <c r="F56">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>55</v>
-      </c>
-      <c r="B57" t="s">
-        <v>72</v>
-      </c>
-      <c r="C57" t="s">
-        <v>70</v>
-      </c>
-      <c r="D57" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" t="s">
-        <v>75</v>
-      </c>
-      <c r="F57">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>55</v>
-      </c>
-      <c r="B58" t="s">
-        <v>72</v>
-      </c>
-      <c r="C58" t="s">
-        <v>70</v>
-      </c>
-      <c r="D58" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" t="s">
-        <v>76</v>
-      </c>
-      <c r="F58">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>55</v>
-      </c>
-      <c r="B59" t="s">
-        <v>72</v>
-      </c>
-      <c r="C59" t="s">
-        <v>70</v>
-      </c>
-      <c r="D59" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" t="s">
-        <v>77</v>
-      </c>
-      <c r="F59">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>52</v>
-      </c>
-      <c r="B60" t="s">
-        <v>78</v>
       </c>
       <c r="C60" t="s">
         <v>70</v>
@@ -2438,24 +2452,24 @@
         <v>20</v>
       </c>
       <c r="E60" t="s">
+        <v>71</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>55</v>
+      </c>
+      <c r="B61" t="s">
         <v>72</v>
-      </c>
-      <c r="F60">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>52</v>
-      </c>
-      <c r="B61" t="s">
-        <v>78</v>
       </c>
       <c r="C61" t="s">
         <v>70</v>
       </c>
       <c r="D61" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E61" t="s">
         <v>73</v>
@@ -2464,18 +2478,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C62" t="s">
         <v>70</v>
       </c>
       <c r="D62" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E62" t="s">
         <v>74</v>
@@ -2484,18 +2498,18 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C63" t="s">
         <v>70</v>
       </c>
       <c r="D63" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E63" t="s">
         <v>75</v>
@@ -2504,18 +2518,18 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B64" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C64" t="s">
         <v>70</v>
       </c>
       <c r="D64" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E64" t="s">
         <v>76</v>
@@ -2524,18 +2538,18 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C65" t="s">
         <v>70</v>
       </c>
       <c r="D65" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E65" t="s">
         <v>77</v>
@@ -2544,272 +2558,272 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C66" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D66" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E66" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C67" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D67" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F67">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C68" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D68" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F68">
         <v>0.5</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C69" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D69" t="s">
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C70" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D70" t="s">
         <v>20</v>
       </c>
       <c r="E70" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F70">
         <v>0.5</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C71" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D71" t="s">
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F71">
         <v>0.5</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
+        <v>60</v>
+      </c>
+      <c r="B72" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" t="s">
+        <v>80</v>
+      </c>
+      <c r="D72" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" t="s">
+        <v>81</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>60</v>
+      </c>
+      <c r="B73" t="s">
+        <v>79</v>
+      </c>
+      <c r="C73" t="s">
+        <v>80</v>
+      </c>
+      <c r="D73" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" t="s">
+        <v>82</v>
+      </c>
+      <c r="F73">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>60</v>
+      </c>
+      <c r="B74" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" t="s">
+        <v>80</v>
+      </c>
+      <c r="D74" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" t="s">
+        <v>83</v>
+      </c>
+      <c r="F74">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>57</v>
+      </c>
+      <c r="B75" t="s">
+        <v>84</v>
+      </c>
+      <c r="C75" t="s">
+        <v>80</v>
+      </c>
+      <c r="D75" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" t="s">
+        <v>81</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>57</v>
+      </c>
+      <c r="B76" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" t="s">
+        <v>80</v>
+      </c>
+      <c r="D76" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" t="s">
+        <v>82</v>
+      </c>
+      <c r="F76">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>57</v>
+      </c>
+      <c r="B77" t="s">
+        <v>84</v>
+      </c>
+      <c r="C77" t="s">
+        <v>80</v>
+      </c>
+      <c r="D77" t="s">
+        <v>20</v>
+      </c>
+      <c r="E77" t="s">
+        <v>83</v>
+      </c>
+      <c r="F77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78">
         <v>1647</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>85</v>
-      </c>
-      <c r="C72" t="s">
-        <v>86</v>
-      </c>
-      <c r="D72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E72" t="s">
-        <v>87</v>
-      </c>
-      <c r="F72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>1647</v>
-      </c>
-      <c r="B73" t="s">
-        <v>85</v>
-      </c>
-      <c r="C73" t="s">
-        <v>86</v>
-      </c>
-      <c r="D73" t="s">
-        <v>20</v>
-      </c>
-      <c r="E73" t="s">
-        <v>88</v>
-      </c>
-      <c r="F73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>1647</v>
-      </c>
-      <c r="B74" t="s">
-        <v>85</v>
-      </c>
-      <c r="C74" t="s">
-        <v>86</v>
-      </c>
-      <c r="D74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E74" t="s">
-        <v>89</v>
-      </c>
-      <c r="F74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <v>89</v>
-      </c>
-      <c r="B75" t="s">
-        <v>90</v>
-      </c>
-      <c r="C75" t="s">
-        <v>86</v>
-      </c>
-      <c r="D75" t="s">
-        <v>20</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <v>65</v>
-      </c>
-      <c r="B76" t="s">
-        <v>91</v>
-      </c>
-      <c r="C76" t="s">
-        <v>86</v>
-      </c>
-      <c r="D76" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" t="s">
-        <v>92</v>
-      </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>65</v>
-      </c>
-      <c r="B77" t="s">
-        <v>91</v>
-      </c>
-      <c r="C77" t="s">
-        <v>86</v>
-      </c>
-      <c r="D77" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" t="s">
-        <v>87</v>
-      </c>
-      <c r="F77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <v>65</v>
-      </c>
-      <c r="B78" t="s">
-        <v>91</v>
       </c>
       <c r="C78" t="s">
         <v>86</v>
       </c>
       <c r="D78" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>64</v>
+        <v>1647</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C79" t="s">
         <v>86</v>
@@ -2818,18 +2832,18 @@
         <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>64</v>
+        <v>1647</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C80" t="s">
         <v>86</v>
@@ -2838,18 +2852,18 @@
         <v>20</v>
       </c>
       <c r="E80" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C81" t="s">
         <v>86</v>
@@ -2858,198 +2872,198 @@
         <v>20</v>
       </c>
       <c r="E81" t="s">
+        <v>7</v>
+      </c>
+      <c r="F81" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>65</v>
+      </c>
+      <c r="B82" t="s">
+        <v>91</v>
+      </c>
+      <c r="C82" t="s">
+        <v>86</v>
+      </c>
+      <c r="D82" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" t="s">
+        <v>92</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>65</v>
+      </c>
+      <c r="B83" t="s">
+        <v>91</v>
+      </c>
+      <c r="C83" t="s">
+        <v>86</v>
+      </c>
+      <c r="D83" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" t="s">
+        <v>87</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>65</v>
+      </c>
+      <c r="B84" t="s">
+        <v>91</v>
+      </c>
+      <c r="C84" t="s">
+        <v>86</v>
+      </c>
+      <c r="D84" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" t="s">
         <v>89</v>
       </c>
-      <c r="F81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A82">
+      <c r="F84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>64</v>
+      </c>
+      <c r="B85" t="s">
+        <v>93</v>
+      </c>
+      <c r="C85" t="s">
+        <v>86</v>
+      </c>
+      <c r="D85" t="s">
+        <v>20</v>
+      </c>
+      <c r="E85" t="s">
+        <v>92</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>64</v>
+      </c>
+      <c r="B86" t="s">
+        <v>93</v>
+      </c>
+      <c r="C86" t="s">
+        <v>86</v>
+      </c>
+      <c r="D86" t="s">
+        <v>20</v>
+      </c>
+      <c r="E86" t="s">
+        <v>87</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>64</v>
+      </c>
+      <c r="B87" t="s">
+        <v>93</v>
+      </c>
+      <c r="C87" t="s">
+        <v>86</v>
+      </c>
+      <c r="D87" t="s">
+        <v>20</v>
+      </c>
+      <c r="E87" t="s">
+        <v>89</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88">
         <v>67</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B88" t="s">
         <v>94</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C88" t="s">
         <v>95</v>
       </c>
-      <c r="D82" t="s">
-        <v>20</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="D88" t="s">
+        <v>20</v>
+      </c>
+      <c r="E88" t="s">
         <v>96</v>
       </c>
-      <c r="F82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A83">
+      <c r="F88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89">
         <v>68</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B89" t="s">
         <v>97</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C89" t="s">
         <v>95</v>
       </c>
-      <c r="D83" t="s">
-        <v>20</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="D89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E89" t="s">
         <v>98</v>
       </c>
-      <c r="F83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A84">
+      <c r="F89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90">
         <v>86</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B90" t="s">
         <v>99</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C90" t="s">
         <v>95</v>
       </c>
-      <c r="D84" t="s">
-        <v>20</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="D90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E90" t="s">
         <v>100</v>
       </c>
-      <c r="F84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A85">
+      <c r="F90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91">
         <v>83</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B91" t="s">
         <v>101</v>
-      </c>
-      <c r="C85" t="s">
-        <v>102</v>
-      </c>
-      <c r="D85" t="s">
-        <v>8</v>
-      </c>
-      <c r="E85" t="s">
-        <v>103</v>
-      </c>
-      <c r="F85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A86">
-        <v>83</v>
-      </c>
-      <c r="B86" t="s">
-        <v>101</v>
-      </c>
-      <c r="C86" t="s">
-        <v>102</v>
-      </c>
-      <c r="D86" t="s">
-        <v>8</v>
-      </c>
-      <c r="E86" t="s">
-        <v>104</v>
-      </c>
-      <c r="F86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A87">
-        <v>83</v>
-      </c>
-      <c r="B87" t="s">
-        <v>101</v>
-      </c>
-      <c r="C87" t="s">
-        <v>102</v>
-      </c>
-      <c r="D87" t="s">
-        <v>8</v>
-      </c>
-      <c r="E87" t="s">
-        <v>105</v>
-      </c>
-      <c r="F87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>83</v>
-      </c>
-      <c r="B88" t="s">
-        <v>101</v>
-      </c>
-      <c r="C88" t="s">
-        <v>102</v>
-      </c>
-      <c r="D88" t="s">
-        <v>8</v>
-      </c>
-      <c r="E88" t="s">
-        <v>106</v>
-      </c>
-      <c r="F88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <v>35</v>
-      </c>
-      <c r="B89" t="s">
-        <v>107</v>
-      </c>
-      <c r="C89" t="s">
-        <v>102</v>
-      </c>
-      <c r="D89" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" t="s">
-        <v>108</v>
-      </c>
-      <c r="F89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <v>35</v>
-      </c>
-      <c r="B90" t="s">
-        <v>107</v>
-      </c>
-      <c r="C90" t="s">
-        <v>102</v>
-      </c>
-      <c r="D90" t="s">
-        <v>8</v>
-      </c>
-      <c r="E90" t="s">
-        <v>109</v>
-      </c>
-      <c r="F90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>35</v>
-      </c>
-      <c r="B91" t="s">
-        <v>107</v>
       </c>
       <c r="C91" t="s">
         <v>102</v>
@@ -3058,18 +3072,18 @@
         <v>8</v>
       </c>
       <c r="E91" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="B92" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C92" t="s">
         <v>102</v>
@@ -3078,38 +3092,38 @@
         <v>8</v>
       </c>
       <c r="E92" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="B93" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C93" t="s">
         <v>102</v>
       </c>
       <c r="D93" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="B94" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C94" t="s">
         <v>102</v>
@@ -3118,18 +3132,18 @@
         <v>8</v>
       </c>
       <c r="E94" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B95" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C95" t="s">
         <v>102</v>
@@ -3138,218 +3152,218 @@
         <v>8</v>
       </c>
       <c r="E95" t="s">
+        <v>108</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>35</v>
+      </c>
+      <c r="B96" t="s">
+        <v>107</v>
+      </c>
+      <c r="C96" t="s">
+        <v>102</v>
+      </c>
+      <c r="D96" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" t="s">
+        <v>109</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>35</v>
+      </c>
+      <c r="B97" t="s">
+        <v>107</v>
+      </c>
+      <c r="C97" t="s">
+        <v>102</v>
+      </c>
+      <c r="D97" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" t="s">
+        <v>110</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>35</v>
+      </c>
+      <c r="B98" t="s">
+        <v>107</v>
+      </c>
+      <c r="C98" t="s">
+        <v>102</v>
+      </c>
+      <c r="D98" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" t="s">
         <v>106</v>
       </c>
-      <c r="F95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A96">
+      <c r="F98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>33</v>
+      </c>
+      <c r="B99" t="s">
+        <v>111</v>
+      </c>
+      <c r="C99" t="s">
+        <v>102</v>
+      </c>
+      <c r="D99" t="s">
+        <v>20</v>
+      </c>
+      <c r="E99" t="s">
+        <v>106</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>36</v>
+      </c>
+      <c r="B100" t="s">
+        <v>112</v>
+      </c>
+      <c r="C100" t="s">
+        <v>102</v>
+      </c>
+      <c r="D100" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" t="s">
+        <v>113</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>36</v>
+      </c>
+      <c r="B101" t="s">
+        <v>112</v>
+      </c>
+      <c r="C101" t="s">
+        <v>102</v>
+      </c>
+      <c r="D101" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" t="s">
+        <v>106</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102">
         <v>1652</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B102" t="s">
         <v>114</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C102" t="s">
         <v>115</v>
       </c>
-      <c r="D96" t="s">
-        <v>20</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="D102" t="s">
+        <v>20</v>
+      </c>
+      <c r="E102" t="s">
         <v>116</v>
       </c>
-      <c r="F96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97">
+      <c r="F102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103">
         <v>1642</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B103" t="s">
         <v>117</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C103" t="s">
         <v>115</v>
       </c>
-      <c r="D97" t="s">
-        <v>20</v>
-      </c>
-      <c r="E97" t="s">
+      <c r="D103" t="s">
+        <v>20</v>
+      </c>
+      <c r="E103" t="s">
         <v>118</v>
       </c>
-      <c r="F97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A98">
+      <c r="F103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104">
         <v>1641</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B104" t="s">
         <v>119</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C104" t="s">
         <v>115</v>
       </c>
-      <c r="D98" t="s">
-        <v>8</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="D104" t="s">
+        <v>8</v>
+      </c>
+      <c r="E104" t="s">
         <v>7</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F104" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A99">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105">
         <v>1643</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B105" t="s">
         <v>120</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C105" t="s">
         <v>115</v>
       </c>
-      <c r="D99" t="s">
-        <v>20</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="D105" t="s">
+        <v>20</v>
+      </c>
+      <c r="E105" t="s">
         <v>121</v>
       </c>
-      <c r="F99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A100">
+      <c r="F105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106">
         <v>39</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B106" t="s">
         <v>122</v>
-      </c>
-      <c r="C100" t="s">
-        <v>123</v>
-      </c>
-      <c r="D100" t="s">
-        <v>20</v>
-      </c>
-      <c r="E100" t="s">
-        <v>124</v>
-      </c>
-      <c r="F100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A101">
-        <v>38</v>
-      </c>
-      <c r="B101" t="s">
-        <v>125</v>
-      </c>
-      <c r="C101" t="s">
-        <v>123</v>
-      </c>
-      <c r="D101" t="s">
-        <v>20</v>
-      </c>
-      <c r="E101" t="s">
-        <v>126</v>
-      </c>
-      <c r="F101">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A102">
-        <v>38</v>
-      </c>
-      <c r="B102" t="s">
-        <v>125</v>
-      </c>
-      <c r="C102" t="s">
-        <v>123</v>
-      </c>
-      <c r="D102" t="s">
-        <v>20</v>
-      </c>
-      <c r="E102" t="s">
-        <v>127</v>
-      </c>
-      <c r="F102">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>38</v>
-      </c>
-      <c r="B103" t="s">
-        <v>125</v>
-      </c>
-      <c r="C103" t="s">
-        <v>123</v>
-      </c>
-      <c r="D103" t="s">
-        <v>20</v>
-      </c>
-      <c r="E103" t="s">
-        <v>128</v>
-      </c>
-      <c r="F103">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <v>38</v>
-      </c>
-      <c r="B104" t="s">
-        <v>125</v>
-      </c>
-      <c r="C104" t="s">
-        <v>123</v>
-      </c>
-      <c r="D104" t="s">
-        <v>20</v>
-      </c>
-      <c r="E104" t="s">
-        <v>129</v>
-      </c>
-      <c r="F104">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <v>38</v>
-      </c>
-      <c r="B105" t="s">
-        <v>125</v>
-      </c>
-      <c r="C105" t="s">
-        <v>123</v>
-      </c>
-      <c r="D105" t="s">
-        <v>20</v>
-      </c>
-      <c r="E105" t="s">
-        <v>130</v>
-      </c>
-      <c r="F105">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <v>38</v>
-      </c>
-      <c r="B106" t="s">
-        <v>125</v>
       </c>
       <c r="C106" t="s">
         <v>123</v>
@@ -3358,18 +3372,18 @@
         <v>20</v>
       </c>
       <c r="E106" t="s">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="F106">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B107" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C107" t="s">
         <v>123</v>
@@ -3378,178 +3392,178 @@
         <v>20</v>
       </c>
       <c r="E107" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F107">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B108" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C108" t="s">
         <v>123</v>
       </c>
       <c r="D108" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E108" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B109" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C109" t="s">
         <v>123</v>
       </c>
       <c r="D109" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E109" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B110" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C110" t="s">
         <v>123</v>
       </c>
       <c r="D110" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E110" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="F110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B111" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C111" t="s">
         <v>123</v>
       </c>
       <c r="D111" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E111" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F111">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B112" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C112" t="s">
         <v>123</v>
       </c>
       <c r="D112" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E112" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F112">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B113" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C113" t="s">
         <v>123</v>
       </c>
       <c r="D113" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E113" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F113">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B114" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C114" t="s">
         <v>123</v>
       </c>
       <c r="D114" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E114" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F114">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B115" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C115" t="s">
         <v>123</v>
       </c>
       <c r="D115" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E115" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F115">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B116" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C116" t="s">
         <v>123</v>
@@ -3558,18 +3572,18 @@
         <v>8</v>
       </c>
       <c r="E116" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="F116">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B117" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C117" t="s">
         <v>123</v>
@@ -3578,18 +3592,18 @@
         <v>8</v>
       </c>
       <c r="E117" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="F117">
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B118" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C118" t="s">
         <v>123</v>
@@ -3598,18 +3612,18 @@
         <v>8</v>
       </c>
       <c r="E118" t="s">
-        <v>142</v>
+        <v>197</v>
       </c>
       <c r="F118">
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B119" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C119" t="s">
         <v>123</v>
@@ -3618,298 +3632,298 @@
         <v>8</v>
       </c>
       <c r="E119" t="s">
+        <v>134</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>41</v>
+      </c>
+      <c r="B120" t="s">
+        <v>135</v>
+      </c>
+      <c r="C120" t="s">
+        <v>123</v>
+      </c>
+      <c r="D120" t="s">
+        <v>8</v>
+      </c>
+      <c r="E120" t="s">
+        <v>136</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>42</v>
+      </c>
+      <c r="B121" t="s">
+        <v>137</v>
+      </c>
+      <c r="C121" t="s">
+        <v>123</v>
+      </c>
+      <c r="D121" t="s">
+        <v>8</v>
+      </c>
+      <c r="E121" t="s">
+        <v>197</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>42</v>
+      </c>
+      <c r="B122" t="s">
+        <v>137</v>
+      </c>
+      <c r="C122" t="s">
+        <v>123</v>
+      </c>
+      <c r="D122" t="s">
+        <v>8</v>
+      </c>
+      <c r="E122" t="s">
+        <v>138</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>42</v>
+      </c>
+      <c r="B123" t="s">
+        <v>137</v>
+      </c>
+      <c r="C123" t="s">
+        <v>123</v>
+      </c>
+      <c r="D123" t="s">
+        <v>8</v>
+      </c>
+      <c r="E123" t="s">
+        <v>139</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>42</v>
+      </c>
+      <c r="B124" t="s">
+        <v>137</v>
+      </c>
+      <c r="C124" t="s">
+        <v>123</v>
+      </c>
+      <c r="D124" t="s">
+        <v>8</v>
+      </c>
+      <c r="E124" t="s">
+        <v>140</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>42</v>
+      </c>
+      <c r="B125" t="s">
+        <v>137</v>
+      </c>
+      <c r="C125" t="s">
+        <v>123</v>
+      </c>
+      <c r="D125" t="s">
+        <v>8</v>
+      </c>
+      <c r="E125" t="s">
+        <v>141</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>42</v>
+      </c>
+      <c r="B126" t="s">
+        <v>137</v>
+      </c>
+      <c r="C126" t="s">
+        <v>123</v>
+      </c>
+      <c r="D126" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" t="s">
+        <v>142</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>42</v>
+      </c>
+      <c r="B127" t="s">
+        <v>137</v>
+      </c>
+      <c r="C127" t="s">
+        <v>123</v>
+      </c>
+      <c r="D127" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" t="s">
+        <v>143</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>42</v>
+      </c>
+      <c r="B128" t="s">
+        <v>137</v>
+      </c>
+      <c r="C128" t="s">
+        <v>123</v>
+      </c>
+      <c r="D128" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" t="s">
+        <v>144</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>43</v>
+      </c>
+      <c r="B129" t="s">
+        <v>145</v>
+      </c>
+      <c r="C129" t="s">
+        <v>123</v>
+      </c>
+      <c r="D129" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" t="s">
+        <v>197</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>43</v>
+      </c>
+      <c r="B130" t="s">
+        <v>145</v>
+      </c>
+      <c r="C130" t="s">
+        <v>123</v>
+      </c>
+      <c r="D130" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" t="s">
+        <v>142</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>43</v>
+      </c>
+      <c r="B131" t="s">
+        <v>145</v>
+      </c>
+      <c r="C131" t="s">
+        <v>123</v>
+      </c>
+      <c r="D131" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" t="s">
         <v>146</v>
       </c>
-      <c r="F119">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A120">
+      <c r="F131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132">
         <v>1656</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B132" t="s">
         <v>147</v>
-      </c>
-      <c r="C120" t="s">
-        <v>148</v>
-      </c>
-      <c r="D120" t="s">
-        <v>8</v>
-      </c>
-      <c r="E120" t="s">
-        <v>7</v>
-      </c>
-      <c r="F120" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A121">
-        <v>1657</v>
-      </c>
-      <c r="B121" t="s">
-        <v>149</v>
-      </c>
-      <c r="C121" t="s">
-        <v>148</v>
-      </c>
-      <c r="D121" t="s">
-        <v>8</v>
-      </c>
-      <c r="E121" t="s">
-        <v>7</v>
-      </c>
-      <c r="F121" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A122">
-        <v>84</v>
-      </c>
-      <c r="B122" t="s">
-        <v>150</v>
-      </c>
-      <c r="C122" t="s">
-        <v>148</v>
-      </c>
-      <c r="D122" t="s">
-        <v>20</v>
-      </c>
-      <c r="E122" t="s">
-        <v>151</v>
-      </c>
-      <c r="F122">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A123">
-        <v>84</v>
-      </c>
-      <c r="B123" t="s">
-        <v>150</v>
-      </c>
-      <c r="C123" t="s">
-        <v>148</v>
-      </c>
-      <c r="D123" t="s">
-        <v>20</v>
-      </c>
-      <c r="E123" t="s">
-        <v>152</v>
-      </c>
-      <c r="F123">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A124">
-        <v>71</v>
-      </c>
-      <c r="B124" t="s">
-        <v>153</v>
-      </c>
-      <c r="C124" t="s">
-        <v>148</v>
-      </c>
-      <c r="D124" t="s">
-        <v>8</v>
-      </c>
-      <c r="E124" t="s">
-        <v>154</v>
-      </c>
-      <c r="F124">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A125">
-        <v>71</v>
-      </c>
-      <c r="B125" t="s">
-        <v>153</v>
-      </c>
-      <c r="C125" t="s">
-        <v>148</v>
-      </c>
-      <c r="D125" t="s">
-        <v>8</v>
-      </c>
-      <c r="E125" t="s">
-        <v>152</v>
-      </c>
-      <c r="F125">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A126">
-        <v>72</v>
-      </c>
-      <c r="B126" t="s">
-        <v>155</v>
-      </c>
-      <c r="C126" t="s">
-        <v>148</v>
-      </c>
-      <c r="D126" t="s">
-        <v>8</v>
-      </c>
-      <c r="E126" t="s">
-        <v>156</v>
-      </c>
-      <c r="F126">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A127">
-        <v>72</v>
-      </c>
-      <c r="B127" t="s">
-        <v>155</v>
-      </c>
-      <c r="C127" t="s">
-        <v>148</v>
-      </c>
-      <c r="D127" t="s">
-        <v>8</v>
-      </c>
-      <c r="E127" t="s">
-        <v>157</v>
-      </c>
-      <c r="F127">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A128">
-        <v>72</v>
-      </c>
-      <c r="B128" t="s">
-        <v>155</v>
-      </c>
-      <c r="C128" t="s">
-        <v>148</v>
-      </c>
-      <c r="D128" t="s">
-        <v>8</v>
-      </c>
-      <c r="E128" t="s">
-        <v>158</v>
-      </c>
-      <c r="F128">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A129">
-        <v>72</v>
-      </c>
-      <c r="B129" t="s">
-        <v>155</v>
-      </c>
-      <c r="C129" t="s">
-        <v>148</v>
-      </c>
-      <c r="D129" t="s">
-        <v>8</v>
-      </c>
-      <c r="E129" t="s">
-        <v>152</v>
-      </c>
-      <c r="F129">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A130">
-        <v>70</v>
-      </c>
-      <c r="B130" t="s">
-        <v>159</v>
-      </c>
-      <c r="C130" t="s">
-        <v>148</v>
-      </c>
-      <c r="D130" t="s">
-        <v>20</v>
-      </c>
-      <c r="E130" t="s">
-        <v>154</v>
-      </c>
-      <c r="F130">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A131">
-        <v>70</v>
-      </c>
-      <c r="B131" t="s">
-        <v>159</v>
-      </c>
-      <c r="C131" t="s">
-        <v>148</v>
-      </c>
-      <c r="D131" t="s">
-        <v>20</v>
-      </c>
-      <c r="E131" t="s">
-        <v>158</v>
-      </c>
-      <c r="F131">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A132">
-        <v>70</v>
-      </c>
-      <c r="B132" t="s">
-        <v>159</v>
       </c>
       <c r="C132" t="s">
         <v>148</v>
       </c>
       <c r="D132" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E132" t="s">
-        <v>152</v>
-      </c>
-      <c r="F132">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="F132" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>85</v>
+        <v>1657</v>
       </c>
       <c r="B133" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C133" t="s">
         <v>148</v>
       </c>
       <c r="D133" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E133" t="s">
-        <v>161</v>
-      </c>
-      <c r="F133">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="F133" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B134" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C134" t="s">
         <v>148</v>
@@ -3918,338 +3932,338 @@
         <v>20</v>
       </c>
       <c r="E134" t="s">
+        <v>151</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>84</v>
+      </c>
+      <c r="B135" t="s">
+        <v>150</v>
+      </c>
+      <c r="C135" t="s">
+        <v>148</v>
+      </c>
+      <c r="D135" t="s">
+        <v>20</v>
+      </c>
+      <c r="E135" t="s">
         <v>152</v>
       </c>
-      <c r="F134">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A135">
+      <c r="F135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>71</v>
+      </c>
+      <c r="B136" t="s">
+        <v>153</v>
+      </c>
+      <c r="C136" t="s">
+        <v>148</v>
+      </c>
+      <c r="D136" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" t="s">
+        <v>154</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>71</v>
+      </c>
+      <c r="B137" t="s">
+        <v>153</v>
+      </c>
+      <c r="C137" t="s">
+        <v>148</v>
+      </c>
+      <c r="D137" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" t="s">
+        <v>152</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>72</v>
+      </c>
+      <c r="B138" t="s">
+        <v>155</v>
+      </c>
+      <c r="C138" t="s">
+        <v>148</v>
+      </c>
+      <c r="D138" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" t="s">
+        <v>156</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>72</v>
+      </c>
+      <c r="B139" t="s">
+        <v>155</v>
+      </c>
+      <c r="C139" t="s">
+        <v>148</v>
+      </c>
+      <c r="D139" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" t="s">
+        <v>157</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>72</v>
+      </c>
+      <c r="B140" t="s">
+        <v>155</v>
+      </c>
+      <c r="C140" t="s">
+        <v>148</v>
+      </c>
+      <c r="D140" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" t="s">
+        <v>158</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>72</v>
+      </c>
+      <c r="B141" t="s">
+        <v>155</v>
+      </c>
+      <c r="C141" t="s">
+        <v>148</v>
+      </c>
+      <c r="D141" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" t="s">
+        <v>152</v>
+      </c>
+      <c r="F141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>70</v>
+      </c>
+      <c r="B142" t="s">
+        <v>159</v>
+      </c>
+      <c r="C142" t="s">
+        <v>148</v>
+      </c>
+      <c r="D142" t="s">
+        <v>20</v>
+      </c>
+      <c r="E142" t="s">
+        <v>154</v>
+      </c>
+      <c r="F142">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>70</v>
+      </c>
+      <c r="B143" t="s">
+        <v>159</v>
+      </c>
+      <c r="C143" t="s">
+        <v>148</v>
+      </c>
+      <c r="D143" t="s">
+        <v>20</v>
+      </c>
+      <c r="E143" t="s">
+        <v>158</v>
+      </c>
+      <c r="F143">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>70</v>
+      </c>
+      <c r="B144" t="s">
+        <v>159</v>
+      </c>
+      <c r="C144" t="s">
+        <v>148</v>
+      </c>
+      <c r="D144" t="s">
+        <v>20</v>
+      </c>
+      <c r="E144" t="s">
+        <v>152</v>
+      </c>
+      <c r="F144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>85</v>
+      </c>
+      <c r="B145" t="s">
+        <v>160</v>
+      </c>
+      <c r="C145" t="s">
+        <v>148</v>
+      </c>
+      <c r="D145" t="s">
+        <v>20</v>
+      </c>
+      <c r="E145" t="s">
+        <v>161</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>85</v>
+      </c>
+      <c r="B146" t="s">
+        <v>160</v>
+      </c>
+      <c r="C146" t="s">
+        <v>148</v>
+      </c>
+      <c r="D146" t="s">
+        <v>20</v>
+      </c>
+      <c r="E146" t="s">
+        <v>152</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147">
         <v>1645</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B147" t="s">
         <v>162</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C147" t="s">
         <v>163</v>
       </c>
-      <c r="D135" t="s">
-        <v>8</v>
-      </c>
-      <c r="E135" t="s">
+      <c r="D147" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" t="s">
         <v>164</v>
-      </c>
-      <c r="F135">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A136">
-        <v>1645</v>
-      </c>
-      <c r="B136" t="s">
-        <v>162</v>
-      </c>
-      <c r="C136" t="s">
-        <v>163</v>
-      </c>
-      <c r="D136" t="s">
-        <v>8</v>
-      </c>
-      <c r="E136" t="s">
-        <v>165</v>
-      </c>
-      <c r="F136">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A137">
-        <v>1645</v>
-      </c>
-      <c r="B137" t="s">
-        <v>162</v>
-      </c>
-      <c r="C137" t="s">
-        <v>163</v>
-      </c>
-      <c r="D137" t="s">
-        <v>8</v>
-      </c>
-      <c r="E137" t="s">
-        <v>106</v>
-      </c>
-      <c r="F137">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A138">
-        <v>1645</v>
-      </c>
-      <c r="B138" t="s">
-        <v>162</v>
-      </c>
-      <c r="C138" t="s">
-        <v>163</v>
-      </c>
-      <c r="D138" t="s">
-        <v>8</v>
-      </c>
-      <c r="E138" t="s">
-        <v>166</v>
-      </c>
-      <c r="F138">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A139">
-        <v>77</v>
-      </c>
-      <c r="B139" t="s">
-        <v>167</v>
-      </c>
-      <c r="C139" t="s">
-        <v>168</v>
-      </c>
-      <c r="D139" t="s">
-        <v>8</v>
-      </c>
-      <c r="E139" t="s">
-        <v>169</v>
-      </c>
-      <c r="F139">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A140">
-        <v>77</v>
-      </c>
-      <c r="B140" t="s">
-        <v>167</v>
-      </c>
-      <c r="C140" t="s">
-        <v>168</v>
-      </c>
-      <c r="D140" t="s">
-        <v>8</v>
-      </c>
-      <c r="E140" t="s">
-        <v>170</v>
-      </c>
-      <c r="F140">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A141">
-        <v>77</v>
-      </c>
-      <c r="B141" t="s">
-        <v>167</v>
-      </c>
-      <c r="C141" t="s">
-        <v>168</v>
-      </c>
-      <c r="D141" t="s">
-        <v>8</v>
-      </c>
-      <c r="E141" t="s">
-        <v>171</v>
-      </c>
-      <c r="F141">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A142">
-        <v>77</v>
-      </c>
-      <c r="B142" t="s">
-        <v>167</v>
-      </c>
-      <c r="C142" t="s">
-        <v>168</v>
-      </c>
-      <c r="D142" t="s">
-        <v>8</v>
-      </c>
-      <c r="E142" t="s">
-        <v>172</v>
-      </c>
-      <c r="F142">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A143">
-        <v>78</v>
-      </c>
-      <c r="B143" t="s">
-        <v>173</v>
-      </c>
-      <c r="C143" t="s">
-        <v>168</v>
-      </c>
-      <c r="D143" t="s">
-        <v>8</v>
-      </c>
-      <c r="E143" t="s">
-        <v>174</v>
-      </c>
-      <c r="F143">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A144">
-        <v>78</v>
-      </c>
-      <c r="B144" t="s">
-        <v>173</v>
-      </c>
-      <c r="C144" t="s">
-        <v>168</v>
-      </c>
-      <c r="D144" t="s">
-        <v>8</v>
-      </c>
-      <c r="E144" t="s">
-        <v>175</v>
-      </c>
-      <c r="F144">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A145">
-        <v>78</v>
-      </c>
-      <c r="B145" t="s">
-        <v>173</v>
-      </c>
-      <c r="C145" t="s">
-        <v>168</v>
-      </c>
-      <c r="D145" t="s">
-        <v>8</v>
-      </c>
-      <c r="E145" t="s">
-        <v>176</v>
-      </c>
-      <c r="F145">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A146">
-        <v>78</v>
-      </c>
-      <c r="B146" t="s">
-        <v>173</v>
-      </c>
-      <c r="C146" t="s">
-        <v>168</v>
-      </c>
-      <c r="D146" t="s">
-        <v>8</v>
-      </c>
-      <c r="E146" t="s">
-        <v>177</v>
-      </c>
-      <c r="F146">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A147">
-        <v>78</v>
-      </c>
-      <c r="B147" t="s">
-        <v>173</v>
-      </c>
-      <c r="C147" t="s">
-        <v>168</v>
-      </c>
-      <c r="D147" t="s">
-        <v>8</v>
-      </c>
-      <c r="E147" t="s">
-        <v>178</v>
       </c>
       <c r="F147">
         <v>0.5</v>
       </c>
     </row>
-    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>78</v>
+        <v>1645</v>
       </c>
       <c r="B148" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C148" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D148" t="s">
         <v>8</v>
       </c>
       <c r="E148" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="F148">
         <v>0.5</v>
       </c>
     </row>
-    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>79</v>
+        <v>1645</v>
       </c>
       <c r="B149" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="C149" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D149" t="s">
         <v>8</v>
       </c>
       <c r="E149" t="s">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="F149">
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>79</v>
+        <v>1645</v>
       </c>
       <c r="B150" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="C150" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D150" t="s">
         <v>8</v>
       </c>
       <c r="E150" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="F150">
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B151" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C151" t="s">
         <v>168</v>
@@ -4258,18 +4272,18 @@
         <v>8</v>
       </c>
       <c r="E151" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="F151">
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B152" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C152" t="s">
         <v>168</v>
@@ -4278,18 +4292,18 @@
         <v>8</v>
       </c>
       <c r="E152" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F152">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B153" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C153" t="s">
         <v>168</v>
@@ -4298,18 +4312,18 @@
         <v>8</v>
       </c>
       <c r="E153" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="F153">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B154" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C154" t="s">
         <v>168</v>
@@ -4318,18 +4332,18 @@
         <v>8</v>
       </c>
       <c r="E154" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="F154">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B155" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C155" t="s">
         <v>168</v>
@@ -4338,18 +4352,18 @@
         <v>8</v>
       </c>
       <c r="E155" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="F155">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B156" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="C156" t="s">
         <v>168</v>
@@ -4358,18 +4372,18 @@
         <v>8</v>
       </c>
       <c r="E156" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B157" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="C157" t="s">
         <v>168</v>
@@ -4378,258 +4392,258 @@
         <v>8</v>
       </c>
       <c r="E157" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B158" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="C158" t="s">
         <v>168</v>
       </c>
       <c r="D158" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E158" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B159" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="C159" t="s">
         <v>168</v>
       </c>
       <c r="D159" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E159" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F159">
         <v>0.5</v>
       </c>
     </row>
-    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B160" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="C160" t="s">
         <v>168</v>
       </c>
       <c r="D160" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E160" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="F160">
         <v>0.5</v>
       </c>
     </row>
-    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B161" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C161" t="s">
         <v>168</v>
       </c>
       <c r="D161" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E161" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B162" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C162" t="s">
         <v>168</v>
       </c>
       <c r="D162" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E162" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B163" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C163" t="s">
         <v>168</v>
       </c>
       <c r="D163" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E163" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F163">
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B164" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C164" t="s">
         <v>168</v>
       </c>
       <c r="D164" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E164" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B165" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C165" t="s">
         <v>168</v>
       </c>
       <c r="D165" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E165" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F165">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B166" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C166" t="s">
         <v>168</v>
       </c>
       <c r="D166" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E166" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F166">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B167" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C167" t="s">
         <v>168</v>
       </c>
       <c r="D167" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E167" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="F167">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B168" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C168" t="s">
         <v>168</v>
       </c>
       <c r="D168" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E168" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B169" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C169" t="s">
         <v>168</v>
       </c>
       <c r="D169" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E169" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F169">
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B170" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C170" t="s">
         <v>168</v>
@@ -4638,18 +4652,18 @@
         <v>20</v>
       </c>
       <c r="E170" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B171" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C171" t="s">
         <v>168</v>
@@ -4658,18 +4672,18 @@
         <v>20</v>
       </c>
       <c r="E171" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F171">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B172" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C172" t="s">
         <v>168</v>
@@ -4678,18 +4692,18 @@
         <v>20</v>
       </c>
       <c r="E172" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="F172">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C173" t="s">
         <v>168</v>
@@ -4698,18 +4712,18 @@
         <v>20</v>
       </c>
       <c r="E173" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="F173">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C174" t="s">
         <v>168</v>
@@ -4718,18 +4732,18 @@
         <v>20</v>
       </c>
       <c r="E174" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="F174">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B175" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C175" t="s">
         <v>168</v>
@@ -4738,18 +4752,18 @@
         <v>20</v>
       </c>
       <c r="E175" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F175">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B176" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C176" t="s">
         <v>168</v>
@@ -4758,18 +4772,18 @@
         <v>20</v>
       </c>
       <c r="E176" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F176">
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B177" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C177" t="s">
         <v>168</v>
@@ -4778,18 +4792,18 @@
         <v>20</v>
       </c>
       <c r="E177" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F177">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B178" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C178" t="s">
         <v>168</v>
@@ -4798,18 +4812,18 @@
         <v>20</v>
       </c>
       <c r="E178" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F178">
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B179" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C179" t="s">
         <v>168</v>
@@ -4818,20 +4832,13 @@
         <v>20</v>
       </c>
       <c r="E179" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F179">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F179" xr:uid="{AF7ADCA9-084A-4F6A-B07C-E2482E2DBBC6}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="HD Plant"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4844,4 +4851,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{4341df80-fbe6-41bf-89b0-e6e2379c9c23}" enabled="0" method="" siteId="{4341df80-fbe6-41bf-89b0-e6e2379c9c23}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/Main Input Files/LP MSF mapping.xlsx
+++ b/Main Input Files/LP MSF mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://riotinto-my.sharepoint.com/personal/oliver_lartigue_riotinto_com/Documents/Documents/31. Tool for LP SL computation/Main Input Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{9196A4BE-9526-4D37-A78A-11F0745B5C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79351E54-9BB8-4F5A-9C4D-D57A5CAAAE74}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{9196A4BE-9526-4D37-A78A-11F0745B5C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{052EF1A2-787B-4CFF-90B3-10F2FF04E441}"/>
   <bookViews>
-    <workbookView xWindow="-12795" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{26E0F985-04E8-41B0-A2C7-BBAD4DDF7EE7}"/>
+    <workbookView xWindow="13140" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{26E0F985-04E8-41B0-A2C7-BBAD4DDF7EE7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="249">
   <si>
     <t>assetGroupingPK</t>
   </si>
@@ -300,18 +300,12 @@
     <t>MDO Plant</t>
   </si>
   <si>
-    <t>Dummy RVY MA Wet Plant</t>
-  </si>
-  <si>
     <t>Mesa A</t>
   </si>
   <si>
     <t>RVAPLTWET</t>
   </si>
   <si>
-    <t>RVAST01</t>
-  </si>
-  <si>
     <t>RVATLO</t>
   </si>
   <si>
@@ -637,6 +631,165 @@
   </si>
   <si>
     <t>MTPCV85C</t>
+  </si>
+  <si>
+    <t>CD2C</t>
+  </si>
+  <si>
+    <t>Car Dumper</t>
+  </si>
+  <si>
+    <t>CLACD2C</t>
+  </si>
+  <si>
+    <t>CD2E</t>
+  </si>
+  <si>
+    <t>EIICD2E</t>
+  </si>
+  <si>
+    <t>UTLNET33KV EII CD2E</t>
+  </si>
+  <si>
+    <t>CD3P</t>
+  </si>
+  <si>
+    <t>PPTCD3P</t>
+  </si>
+  <si>
+    <t>CD4P</t>
+  </si>
+  <si>
+    <t>PPTCD4P</t>
+  </si>
+  <si>
+    <t>CD5C</t>
+  </si>
+  <si>
+    <t>CLBAF52</t>
+  </si>
+  <si>
+    <t>CLBCD5C</t>
+  </si>
+  <si>
+    <t>CLBPOSACD5C</t>
+  </si>
+  <si>
+    <t>CLBSUBCD5C</t>
+  </si>
+  <si>
+    <t>CD6C</t>
+  </si>
+  <si>
+    <t>CLBAF61</t>
+  </si>
+  <si>
+    <t>CLBAF62</t>
+  </si>
+  <si>
+    <t>CLBCD6C</t>
+  </si>
+  <si>
+    <t>CLBSUBCD6C</t>
+  </si>
+  <si>
+    <t>CD7C</t>
+  </si>
+  <si>
+    <t>CLBCD7C</t>
+  </si>
+  <si>
+    <t>CLBSUBCD7C</t>
+  </si>
+  <si>
+    <t>YA Plant 3</t>
+  </si>
+  <si>
+    <t>Yandi Loop Plant</t>
+  </si>
+  <si>
+    <t>SL11C</t>
+  </si>
+  <si>
+    <t>Ship Loader</t>
+  </si>
+  <si>
+    <t>CLBBTH05</t>
+  </si>
+  <si>
+    <t>CLBBTH06</t>
+  </si>
+  <si>
+    <t>CLBSLD11C</t>
+  </si>
+  <si>
+    <t>SL12C</t>
+  </si>
+  <si>
+    <t>CLBBTH07</t>
+  </si>
+  <si>
+    <t>CLBBTH08</t>
+  </si>
+  <si>
+    <t>CLBSLD12C</t>
+  </si>
+  <si>
+    <t>SL1E</t>
+  </si>
+  <si>
+    <t>EIIBTHLAYBY</t>
+  </si>
+  <si>
+    <t>EIISLD1E</t>
+  </si>
+  <si>
+    <t>SL2C</t>
+  </si>
+  <si>
+    <t>CLABTH03</t>
+  </si>
+  <si>
+    <t>CLABTH04</t>
+  </si>
+  <si>
+    <t>CLASLD2C</t>
+  </si>
+  <si>
+    <t>SL2P</t>
+  </si>
+  <si>
+    <t>PPTBTH04</t>
+  </si>
+  <si>
+    <t>PPTBTH05</t>
+  </si>
+  <si>
+    <t>PPTSLD2P</t>
+  </si>
+  <si>
+    <t>SL3C</t>
+  </si>
+  <si>
+    <t>CLABTH01</t>
+  </si>
+  <si>
+    <t>CLABTH02</t>
+  </si>
+  <si>
+    <t>CLASLD3C</t>
+  </si>
+  <si>
+    <t>SL3P</t>
+  </si>
+  <si>
+    <t>PPTBTH02</t>
+  </si>
+  <si>
+    <t>PPTBTH03</t>
+  </si>
+  <si>
+    <t>PPTSLD3P</t>
   </si>
 </sst>
 </file>
@@ -795,7 +948,20 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>SELECT DISTINCT (AMFP.[assetGroupingPK])</a:t>
+            <a:t>SELECT </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>DISTINCT (AMFP.[assetGroupingPK])</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -847,7 +1013,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>      ,AMFP.[MSFName]</a:t>
+            <a:t>    ,AMFP.[MSFName]</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -860,7 +1026,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>      ,AMFP.[percentageImpact]</a:t>
+            <a:t>    ,AMFP.[percentageImpact]</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -912,7 +1078,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>  WHERE AMFP.[assetClassName] IN ('Plant','Primary Crusher')</a:t>
+            <a:t>  WHERE </a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -925,7 +1091,33 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>  ORDER BY PG.[planningGroupName], AG.[assetGroupingName]</a:t>
+            <a:t>AMFP.[assetClassName] IN ('Plant','Primary Crusher') AND AG.[assetGroupingName] NOT IN ('Dummy RVY MA Wet Plant') OR</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>AG.[assetGroupingName] IN ('CD2E', 'CD3P', 'CD4P', 'CD2C', 'CD5C', 'CD6C', 'CD7C', 'SL1E', 'SL2P', 'SL3P', 'SL2C', 'SL3C', 'SL11C', 'SL12C')</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>  ORDER BY AMFP.[assetClassName], PG.[planningGroupName], AG.[assetGroupingName]</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1252,7 +1444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF7ADCA9-084A-4F6A-B07C-E2482E2DBBC6}">
-  <dimension ref="A1:F179"/>
+  <dimension ref="A1:F223"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="6" width="21.109375" customWidth="1"/>
@@ -1280,19 +1472,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1502</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>196</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>197</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>198</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1300,19 +1492,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1502</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>199</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>197</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1320,19 +1512,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>199</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>197</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1340,19 +1532,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>202</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>197</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>203</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1360,19 +1552,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>197</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>205</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1380,19 +1572,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>197</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>207</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1400,19 +1592,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1618</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>197</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>208</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1420,19 +1612,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1618</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>197</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>209</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1440,79 +1632,79 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>206</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>210</v>
       </c>
       <c r="F10">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>212</v>
       </c>
       <c r="F11">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>213</v>
       </c>
       <c r="F12">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1520,62 +1712,62 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="E14" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="F14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>216</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="E15" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="F15">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>216</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="E16" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="F16">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1592,7 +1784,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>194</v>
+        <v>13</v>
       </c>
       <c r="F17">
         <v>0.1</v>
@@ -1612,7 +1804,7 @@
         <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>195</v>
+        <v>16</v>
       </c>
       <c r="F18">
         <v>0.1</v>
@@ -1632,7 +1824,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="F19">
         <v>0.1</v>
@@ -1640,19 +1832,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D20" t="s">
         <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1660,139 +1852,139 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s">
         <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>189</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
       <c r="F22">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>191</v>
       </c>
       <c r="F23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s">
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>7</v>
+        <v>193</v>
+      </c>
+      <c r="F25">
+        <v>0.1</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>194</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
         <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -1800,10 +1992,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
         <v>22</v>
@@ -1812,7 +2004,7 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -1820,10 +2012,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
         <v>22</v>
@@ -1832,18 +2024,18 @@
         <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F29">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
         <v>22</v>
@@ -1852,18 +2044,18 @@
         <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F30">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
         <v>22</v>
@@ -1872,18 +2064,18 @@
         <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F31">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
         <v>22</v>
@@ -1892,10 +2084,10 @@
         <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32">
-        <v>0.25</v>
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1912,10 +2104,10 @@
         <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1932,110 +2124,110 @@
         <v>20</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F34">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
         <v>22</v>
       </c>
       <c r="D35" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
         <v>22</v>
       </c>
       <c r="D36" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D37" t="s">
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D38" t="s">
         <v>20</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F38">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D39" t="s">
         <v>20</v>
       </c>
       <c r="E39" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F39">
-        <v>9.5000000000000001E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2052,10 +2244,10 @@
         <v>20</v>
       </c>
       <c r="E40" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F40">
-        <v>0.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2072,7 +2264,7 @@
         <v>20</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F41">
         <v>0.15</v>
@@ -2092,10 +2284,10 @@
         <v>20</v>
       </c>
       <c r="E42" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F42">
-        <v>0.15</v>
+        <v>9.5000000000000001E-2</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2112,10 +2304,10 @@
         <v>20</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F43">
-        <v>9.5000000000000001E-2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2132,10 +2324,10 @@
         <v>20</v>
       </c>
       <c r="E44" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F44">
-        <v>9.5000000000000001E-2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2152,78 +2344,78 @@
         <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F45">
-        <v>9.5000000000000001E-2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>1651</v>
+        <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D46" t="s">
         <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>7</v>
+        <v>49</v>
+      </c>
+      <c r="F46">
+        <v>9.5000000000000001E-2</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D47" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>9.5000000000000001E-2</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C48" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D48" t="s">
         <v>20</v>
       </c>
       <c r="E48" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>9.5000000000000001E-2</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>46</v>
+        <v>1651</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C49" t="s">
         <v>53</v>
@@ -2232,10 +2424,10 @@
         <v>20</v>
       </c>
       <c r="E49" t="s">
-        <v>57</v>
-      </c>
-      <c r="F49">
-        <v>0.1</v>
+        <v>7</v>
+      </c>
+      <c r="F49" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2252,18 +2444,18 @@
         <v>20</v>
       </c>
       <c r="E50" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F50">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>1644</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C51" t="s">
         <v>53</v>
@@ -2272,18 +2464,18 @@
         <v>20</v>
       </c>
       <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>7</v>
+        <v>57</v>
+      </c>
+      <c r="F51">
+        <v>0.1</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
         <v>53</v>
@@ -2292,47 +2484,47 @@
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>49</v>
+        <v>1644</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D53" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>64</v>
-      </c>
-      <c r="F53">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="F53" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D54" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E54" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -2340,42 +2532,42 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C55" t="s">
         <v>63</v>
       </c>
       <c r="D55" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E55" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s">
         <v>63</v>
       </c>
       <c r="D56" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -2392,58 +2584,58 @@
         <v>20</v>
       </c>
       <c r="E57" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F57">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>48</v>
+        <v>1653</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C58" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D58" t="s">
         <v>20</v>
       </c>
       <c r="E58" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F58">
-        <v>0.28999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D59" t="s">
         <v>20</v>
       </c>
       <c r="E59" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>1653</v>
+        <v>52</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
         <v>70</v>
@@ -2452,7 +2644,7 @@
         <v>20</v>
       </c>
       <c r="E60" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -2460,39 +2652,39 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C61" t="s">
         <v>70</v>
       </c>
       <c r="D61" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E61" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C62" t="s">
         <v>70</v>
       </c>
       <c r="D62" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E62" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F62">
         <v>0.5</v>
@@ -2500,19 +2692,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B63" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C63" t="s">
         <v>70</v>
       </c>
       <c r="D63" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E63" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F63">
         <v>0.5</v>
@@ -2520,19 +2712,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C64" t="s">
         <v>70</v>
       </c>
       <c r="D64" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F64">
         <v>0.5</v>
@@ -2540,39 +2732,39 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C65" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D65" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E65" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F65">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C66" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D66" t="s">
         <v>20</v>
       </c>
       <c r="E66" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="F66">
         <v>0.5</v>
@@ -2580,119 +2772,119 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B67" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C67" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D67" t="s">
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C68" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D68" t="s">
         <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>74</v>
-      </c>
-      <c r="F68">
-        <v>0.5</v>
+        <v>7</v>
+      </c>
+      <c r="F68" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B69" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C69" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D69" t="s">
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F69">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C70" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D70" t="s">
         <v>20</v>
       </c>
       <c r="E70" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F70">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B71" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C71" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D71" t="s">
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F71">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C72" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D72" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E72" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -2700,59 +2892,59 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B73" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="C73" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D73" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E73" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F73">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="B74" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D74" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E74" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="F74">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C75" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D75" t="s">
         <v>20</v>
       </c>
       <c r="E75" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -2760,59 +2952,59 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>57</v>
+        <v>1652</v>
       </c>
       <c r="B76" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C76" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="D76" t="s">
         <v>20</v>
       </c>
       <c r="E76" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="F76">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>57</v>
+        <v>1642</v>
       </c>
       <c r="B77" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="C77" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="D77" t="s">
         <v>20</v>
       </c>
       <c r="E77" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="F77">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>1647</v>
+        <v>1643</v>
       </c>
       <c r="B78" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="C78" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="D78" t="s">
         <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -2820,19 +3012,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>1647</v>
+        <v>39</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="C79" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D79" t="s">
         <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>88</v>
+        <v>195</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -2840,19 +3032,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>1647</v>
+        <v>39</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="C80" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D80" t="s">
         <v>20</v>
       </c>
       <c r="E80" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -2860,39 +3052,39 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="B81" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="C81" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D81" t="s">
         <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>7</v>
-      </c>
-      <c r="F81" t="s">
-        <v>7</v>
+        <v>195</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="B82" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="C82" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D82" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -2900,139 +3092,139 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="B83" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="C83" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D83" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="B84" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="C84" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D84" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E84" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="C85" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D85" t="s">
         <v>20</v>
       </c>
       <c r="E85" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B86" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="C86" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D86" t="s">
         <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="C87" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D87" t="s">
         <v>20</v>
       </c>
       <c r="E87" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="B88" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="C88" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="D88" t="s">
         <v>20</v>
       </c>
       <c r="E88" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B89" t="s">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="C89" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="D89" t="s">
         <v>20</v>
       </c>
       <c r="E89" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -3040,19 +3232,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B90" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="C90" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="D90" t="s">
         <v>20</v>
       </c>
       <c r="E90" t="s">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -3060,59 +3252,59 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B91" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="C91" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="D91" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E91" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B92" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="C92" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="D92" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E92" t="s">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B93" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="C93" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="D93" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E93" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -3120,19 +3312,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B94" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="C94" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="D94" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E94" t="s">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="F94">
         <v>1</v>
@@ -3140,19 +3332,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="C95" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="D95" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E95" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="F95">
         <v>1</v>
@@ -3160,19 +3352,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>186</v>
       </c>
       <c r="C96" t="s">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="D96" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E96" t="s">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="F96">
         <v>1</v>
@@ -3180,59 +3372,59 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="B97" t="s">
-        <v>107</v>
+        <v>186</v>
       </c>
       <c r="C97" t="s">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="D97" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E97" t="s">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="B98" t="s">
-        <v>107</v>
+        <v>186</v>
       </c>
       <c r="C98" t="s">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="D98" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E98" t="s">
-        <v>106</v>
+        <v>169</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="B99" t="s">
-        <v>111</v>
+        <v>186</v>
       </c>
       <c r="C99" t="s">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="D99" t="s">
         <v>20</v>
       </c>
       <c r="E99" t="s">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -3240,19 +3432,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="B100" t="s">
-        <v>112</v>
+        <v>187</v>
       </c>
       <c r="C100" t="s">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="D100" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E100" t="s">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="F100">
         <v>1</v>
@@ -3260,19 +3452,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="B101" t="s">
-        <v>112</v>
+        <v>187</v>
       </c>
       <c r="C101" t="s">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="D101" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E101" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -3280,19 +3472,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>1652</v>
+        <v>75</v>
       </c>
       <c r="B102" t="s">
-        <v>114</v>
+        <v>187</v>
       </c>
       <c r="C102" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="D102" t="s">
         <v>20</v>
       </c>
       <c r="E102" t="s">
-        <v>116</v>
+        <v>188</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -3300,19 +3492,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>1642</v>
+        <v>75</v>
       </c>
       <c r="B103" t="s">
-        <v>117</v>
+        <v>187</v>
       </c>
       <c r="C103" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="D103" t="s">
         <v>20</v>
       </c>
       <c r="E103" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -3320,59 +3512,59 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>1641</v>
+        <v>75</v>
       </c>
       <c r="B104" t="s">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="C104" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="D104" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E104" t="s">
-        <v>7</v>
-      </c>
-      <c r="F104" t="s">
-        <v>7</v>
+        <v>176</v>
+      </c>
+      <c r="F104">
+        <v>0.5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>1643</v>
+        <v>75</v>
       </c>
       <c r="B105" t="s">
-        <v>120</v>
+        <v>187</v>
       </c>
       <c r="C105" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="D105" t="s">
         <v>20</v>
       </c>
       <c r="E105" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="F105">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="B106" t="s">
-        <v>122</v>
+        <v>219</v>
       </c>
       <c r="C106" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D106" t="s">
         <v>20</v>
       </c>
       <c r="E106" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="F106">
         <v>1</v>
@@ -3380,19 +3572,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="B107" t="s">
-        <v>122</v>
+        <v>219</v>
       </c>
       <c r="C107" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D107" t="s">
         <v>20</v>
       </c>
       <c r="E107" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -3400,19 +3592,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B108" t="s">
-        <v>125</v>
+        <v>219</v>
       </c>
       <c r="C108" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D108" t="s">
         <v>20</v>
       </c>
       <c r="E108" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -3420,19 +3612,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B109" t="s">
-        <v>125</v>
+        <v>219</v>
       </c>
       <c r="C109" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D109" t="s">
         <v>20</v>
       </c>
       <c r="E109" t="s">
-        <v>126</v>
+        <v>175</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -3440,159 +3632,159 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B110" t="s">
-        <v>125</v>
+        <v>219</v>
       </c>
       <c r="C110" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D110" t="s">
         <v>20</v>
       </c>
       <c r="E110" t="s">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="F110">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B111" t="s">
-        <v>125</v>
+        <v>219</v>
       </c>
       <c r="C111" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D111" t="s">
         <v>20</v>
       </c>
       <c r="E111" t="s">
-        <v>128</v>
+        <v>183</v>
       </c>
       <c r="F111">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>219</v>
       </c>
       <c r="C112" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D112" t="s">
         <v>20</v>
       </c>
       <c r="E112" t="s">
-        <v>129</v>
+        <v>184</v>
       </c>
       <c r="F112">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="B113" t="s">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="C113" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D113" t="s">
         <v>20</v>
       </c>
       <c r="E113" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="F113">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="B114" t="s">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="C114" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D114" t="s">
         <v>20</v>
       </c>
       <c r="E114" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="F114">
-        <v>0.35</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="B115" t="s">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="C115" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D115" t="s">
         <v>20</v>
       </c>
       <c r="E115" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="F115">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="B116" t="s">
-        <v>133</v>
+        <v>220</v>
       </c>
       <c r="C116" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D116" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E116" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="B117" t="s">
-        <v>133</v>
+        <v>220</v>
       </c>
       <c r="C117" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="D117" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E117" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -3600,19 +3792,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>41</v>
+        <v>1502</v>
       </c>
       <c r="B118" t="s">
-        <v>135</v>
+        <v>6</v>
       </c>
       <c r="C118" t="s">
-        <v>123</v>
+        <v>7</v>
       </c>
       <c r="D118" t="s">
         <v>8</v>
       </c>
       <c r="E118" t="s">
-        <v>197</v>
+        <v>9</v>
       </c>
       <c r="F118">
         <v>1</v>
@@ -3620,19 +3812,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>41</v>
+        <v>1502</v>
       </c>
       <c r="B119" t="s">
-        <v>135</v>
+        <v>6</v>
       </c>
       <c r="C119" t="s">
-        <v>123</v>
+        <v>7</v>
       </c>
       <c r="D119" t="s">
         <v>8</v>
       </c>
       <c r="E119" t="s">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="F119">
         <v>1</v>
@@ -3640,19 +3832,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="B120" t="s">
-        <v>135</v>
+        <v>11</v>
       </c>
       <c r="C120" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="D120" t="s">
         <v>8</v>
       </c>
       <c r="E120" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="F120">
         <v>1</v>
@@ -3660,19 +3852,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="B121" t="s">
-        <v>137</v>
+        <v>11</v>
       </c>
       <c r="C121" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="D121" t="s">
         <v>8</v>
       </c>
       <c r="E121" t="s">
-        <v>197</v>
+        <v>14</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -3680,19 +3872,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="B122" t="s">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="C122" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="D122" t="s">
         <v>8</v>
       </c>
       <c r="E122" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -3700,19 +3892,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="B123" t="s">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="C123" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="D123" t="s">
         <v>8</v>
       </c>
       <c r="E123" t="s">
-        <v>139</v>
+        <v>14</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -3720,19 +3912,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>42</v>
+        <v>1618</v>
       </c>
       <c r="B124" t="s">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c r="C124" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="D124" t="s">
         <v>8</v>
       </c>
       <c r="E124" t="s">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -3740,19 +3932,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>42</v>
+        <v>1618</v>
       </c>
       <c r="B125" t="s">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c r="C125" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="D125" t="s">
         <v>8</v>
       </c>
       <c r="E125" t="s">
-        <v>141</v>
+        <v>14</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -3760,19 +3952,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B126" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="C126" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="D126" t="s">
         <v>8</v>
       </c>
       <c r="E126" t="s">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -3780,19 +3972,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B127" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="C127" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="D127" t="s">
         <v>8</v>
       </c>
       <c r="E127" t="s">
-        <v>143</v>
+        <v>10</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -3800,19 +3992,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B128" t="s">
-        <v>137</v>
+        <v>39</v>
       </c>
       <c r="C128" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="D128" t="s">
         <v>8</v>
       </c>
       <c r="E128" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -3820,19 +4012,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B129" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="C129" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="D129" t="s">
         <v>8</v>
       </c>
       <c r="E129" t="s">
-        <v>197</v>
+        <v>40</v>
       </c>
       <c r="F129">
         <v>1</v>
@@ -3840,19 +4032,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="B130" t="s">
-        <v>145</v>
+        <v>54</v>
       </c>
       <c r="C130" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="D130" t="s">
         <v>8</v>
       </c>
       <c r="E130" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="F130">
         <v>1</v>
@@ -3860,19 +4052,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B131" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="C131" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="D131" t="s">
         <v>8</v>
       </c>
       <c r="E131" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -3880,59 +4072,59 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>1656</v>
+        <v>49</v>
       </c>
       <c r="B132" t="s">
-        <v>147</v>
+        <v>62</v>
       </c>
       <c r="C132" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="D132" t="s">
         <v>8</v>
       </c>
       <c r="E132" t="s">
-        <v>7</v>
-      </c>
-      <c r="F132" t="s">
-        <v>7</v>
+        <v>65</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>1657</v>
+        <v>50</v>
       </c>
       <c r="B133" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="C133" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="D133" t="s">
         <v>8</v>
       </c>
       <c r="E133" t="s">
-        <v>7</v>
-      </c>
-      <c r="F133" t="s">
-        <v>7</v>
+        <v>67</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="B134" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="C134" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="D134" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E134" t="s">
-        <v>151</v>
+        <v>65</v>
       </c>
       <c r="F134">
         <v>1</v>
@@ -3940,19 +4132,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="B135" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="C135" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="D135" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E135" t="s">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -3960,99 +4152,99 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B136" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="C136" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="D136" t="s">
         <v>8</v>
       </c>
       <c r="E136" t="s">
-        <v>154</v>
+        <v>74</v>
       </c>
       <c r="F136">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B137" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="C137" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="D137" t="s">
         <v>8</v>
       </c>
       <c r="E137" t="s">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="F137">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138">
+        <v>55</v>
+      </c>
+      <c r="B138" t="s">
         <v>72</v>
       </c>
-      <c r="B138" t="s">
-        <v>155</v>
-      </c>
       <c r="C138" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="D138" t="s">
         <v>8</v>
       </c>
       <c r="E138" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="F138">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139">
+        <v>55</v>
+      </c>
+      <c r="B139" t="s">
         <v>72</v>
       </c>
-      <c r="B139" t="s">
-        <v>155</v>
-      </c>
       <c r="C139" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="D139" t="s">
         <v>8</v>
       </c>
       <c r="E139" t="s">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="F139">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B140" t="s">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="C140" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="D140" t="s">
         <v>8</v>
       </c>
       <c r="E140" t="s">
-        <v>158</v>
+        <v>81</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -4060,39 +4252,39 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B141" t="s">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="C141" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="D141" t="s">
         <v>8</v>
       </c>
       <c r="E141" t="s">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="F141">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B142" t="s">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="C142" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="D142" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E142" t="s">
-        <v>154</v>
+        <v>83</v>
       </c>
       <c r="F142">
         <v>0.5</v>
@@ -4100,39 +4292,39 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B143" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="C143" t="s">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="D143" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E143" t="s">
-        <v>158</v>
+        <v>90</v>
       </c>
       <c r="F143">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B144" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="C144" t="s">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="D144" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E144" t="s">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -4140,19 +4332,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145">
+        <v>65</v>
+      </c>
+      <c r="B145" t="s">
+        <v>89</v>
+      </c>
+      <c r="C145" t="s">
         <v>85</v>
       </c>
-      <c r="B145" t="s">
-        <v>160</v>
-      </c>
-      <c r="C145" t="s">
-        <v>148</v>
-      </c>
       <c r="D145" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E145" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="F145">
         <v>1</v>
@@ -4160,19 +4352,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B146" t="s">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="C146" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="D146" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E146" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -4180,59 +4372,59 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>1645</v>
+        <v>83</v>
       </c>
       <c r="B147" t="s">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="C147" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="D147" t="s">
         <v>8</v>
       </c>
       <c r="E147" t="s">
-        <v>164</v>
+        <v>102</v>
       </c>
       <c r="F147">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>1645</v>
+        <v>83</v>
       </c>
       <c r="B148" t="s">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="C148" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="D148" t="s">
         <v>8</v>
       </c>
       <c r="E148" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="F148">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>1645</v>
+        <v>83</v>
       </c>
       <c r="B149" t="s">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="C149" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="D149" t="s">
         <v>8</v>
       </c>
       <c r="E149" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F149">
         <v>1</v>
@@ -4240,19 +4432,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>1645</v>
+        <v>35</v>
       </c>
       <c r="B150" t="s">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="C150" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="D150" t="s">
         <v>8</v>
       </c>
       <c r="E150" t="s">
-        <v>166</v>
+        <v>106</v>
       </c>
       <c r="F150">
         <v>1</v>
@@ -4260,19 +4452,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="B151" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="C151" t="s">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="D151" t="s">
         <v>8</v>
       </c>
       <c r="E151" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="F151">
         <v>1</v>
@@ -4280,59 +4472,59 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="B152" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="C152" t="s">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="D152" t="s">
         <v>8</v>
       </c>
       <c r="E152" t="s">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="F152">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="B153" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="C153" t="s">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="D153" t="s">
         <v>8</v>
       </c>
       <c r="E153" t="s">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="F153">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="B154" t="s">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="C154" t="s">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="D154" t="s">
         <v>8</v>
       </c>
       <c r="E154" t="s">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="F154">
         <v>1</v>
@@ -4340,19 +4532,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="B155" t="s">
-        <v>173</v>
+        <v>110</v>
       </c>
       <c r="C155" t="s">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="D155" t="s">
         <v>8</v>
       </c>
       <c r="E155" t="s">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="F155">
         <v>1</v>
@@ -4360,39 +4552,39 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>78</v>
+        <v>1641</v>
       </c>
       <c r="B156" t="s">
-        <v>173</v>
+        <v>117</v>
       </c>
       <c r="C156" t="s">
-        <v>168</v>
+        <v>113</v>
       </c>
       <c r="D156" t="s">
         <v>8</v>
       </c>
       <c r="E156" t="s">
-        <v>175</v>
-      </c>
-      <c r="F156">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="F156" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B157" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="C157" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D157" t="s">
         <v>8</v>
       </c>
       <c r="E157" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="F157">
         <v>1</v>
@@ -4400,19 +4592,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B158" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="C158" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D158" t="s">
         <v>8</v>
       </c>
       <c r="E158" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="F158">
         <v>1</v>
@@ -4420,59 +4612,59 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="B159" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="C159" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D159" t="s">
         <v>8</v>
       </c>
       <c r="E159" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="F159">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="B160" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="C160" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D160" t="s">
         <v>8</v>
       </c>
       <c r="E160" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="F160">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B161" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="C161" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D161" t="s">
         <v>8</v>
       </c>
       <c r="E161" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="F161">
         <v>1</v>
@@ -4480,19 +4672,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B162" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C162" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D162" t="s">
         <v>8</v>
       </c>
       <c r="E162" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="F162">
         <v>1</v>
@@ -4500,19 +4692,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B163" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C163" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D163" t="s">
         <v>8</v>
       </c>
       <c r="E163" t="s">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -4520,19 +4712,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B164" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C164" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D164" t="s">
         <v>8</v>
       </c>
       <c r="E164" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="F164">
         <v>1</v>
@@ -4540,79 +4732,79 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B165" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C165" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D165" t="s">
         <v>8</v>
       </c>
       <c r="E165" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
       <c r="F165">
-        <v>0.33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B166" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C166" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D166" t="s">
         <v>8</v>
       </c>
       <c r="E166" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="F166">
-        <v>0.33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B167" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C167" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D167" t="s">
         <v>8</v>
       </c>
       <c r="E167" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="F167">
-        <v>0.33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B168" t="s">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="C168" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D168" t="s">
         <v>8</v>
       </c>
       <c r="E168" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="F168">
         <v>1</v>
@@ -4620,19 +4812,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B169" t="s">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="C169" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D169" t="s">
         <v>8</v>
       </c>
       <c r="E169" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="F169">
         <v>1</v>
@@ -4640,19 +4832,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B170" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="C170" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D170" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E170" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="F170">
         <v>1</v>
@@ -4660,99 +4852,99 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B171" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="C171" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D171" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E171" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="F171">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B172" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="C172" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D172" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E172" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="F172">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173">
-        <v>74</v>
+        <v>1656</v>
       </c>
       <c r="B173" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="C173" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="D173" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E173" t="s">
-        <v>172</v>
-      </c>
-      <c r="F173">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="F173" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174">
-        <v>75</v>
+        <v>1657</v>
       </c>
       <c r="B174" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="C174" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="D174" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E174" t="s">
-        <v>174</v>
-      </c>
-      <c r="F174">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="F174" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B175" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="C175" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="D175" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E175" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="F175">
         <v>1</v>
@@ -4760,19 +4952,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B176" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="C176" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="D176" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E176" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="F176">
         <v>1</v>
@@ -4780,19 +4972,19 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B177" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="C177" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="D177" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E177" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="F177">
         <v>1</v>
@@ -4800,42 +4992,922 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B178" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="C178" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="D178" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E178" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="F178">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B179" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="C179" t="s">
+        <v>146</v>
+      </c>
+      <c r="D179" t="s">
+        <v>8</v>
+      </c>
+      <c r="E179" t="s">
+        <v>156</v>
+      </c>
+      <c r="F179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>72</v>
+      </c>
+      <c r="B180" t="s">
+        <v>153</v>
+      </c>
+      <c r="C180" t="s">
+        <v>146</v>
+      </c>
+      <c r="D180" t="s">
+        <v>8</v>
+      </c>
+      <c r="E180" t="s">
+        <v>150</v>
+      </c>
+      <c r="F180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>1645</v>
+      </c>
+      <c r="B181" t="s">
+        <v>160</v>
+      </c>
+      <c r="C181" t="s">
+        <v>161</v>
+      </c>
+      <c r="D181" t="s">
+        <v>8</v>
+      </c>
+      <c r="E181" t="s">
+        <v>162</v>
+      </c>
+      <c r="F181">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>1645</v>
+      </c>
+      <c r="B182" t="s">
+        <v>160</v>
+      </c>
+      <c r="C182" t="s">
+        <v>161</v>
+      </c>
+      <c r="D182" t="s">
+        <v>8</v>
+      </c>
+      <c r="E182" t="s">
+        <v>163</v>
+      </c>
+      <c r="F182">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>1645</v>
+      </c>
+      <c r="B183" t="s">
+        <v>160</v>
+      </c>
+      <c r="C183" t="s">
+        <v>161</v>
+      </c>
+      <c r="D183" t="s">
+        <v>8</v>
+      </c>
+      <c r="E183" t="s">
+        <v>104</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>1645</v>
+      </c>
+      <c r="B184" t="s">
+        <v>160</v>
+      </c>
+      <c r="C184" t="s">
+        <v>161</v>
+      </c>
+      <c r="D184" t="s">
+        <v>8</v>
+      </c>
+      <c r="E184" t="s">
+        <v>164</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>77</v>
+      </c>
+      <c r="B185" t="s">
+        <v>165</v>
+      </c>
+      <c r="C185" t="s">
+        <v>166</v>
+      </c>
+      <c r="D185" t="s">
+        <v>8</v>
+      </c>
+      <c r="E185" t="s">
+        <v>167</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>77</v>
+      </c>
+      <c r="B186" t="s">
+        <v>165</v>
+      </c>
+      <c r="C186" t="s">
+        <v>166</v>
+      </c>
+      <c r="D186" t="s">
+        <v>8</v>
+      </c>
+      <c r="E186" t="s">
         <v>168</v>
       </c>
-      <c r="D179" t="s">
-        <v>20</v>
-      </c>
-      <c r="E179" t="s">
+      <c r="F186">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>77</v>
+      </c>
+      <c r="B187" t="s">
+        <v>165</v>
+      </c>
+      <c r="C187" t="s">
+        <v>166</v>
+      </c>
+      <c r="D187" t="s">
+        <v>8</v>
+      </c>
+      <c r="E187" t="s">
+        <v>169</v>
+      </c>
+      <c r="F187">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>77</v>
+      </c>
+      <c r="B188" t="s">
+        <v>165</v>
+      </c>
+      <c r="C188" t="s">
+        <v>166</v>
+      </c>
+      <c r="D188" t="s">
+        <v>8</v>
+      </c>
+      <c r="E188" t="s">
+        <v>170</v>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>78</v>
+      </c>
+      <c r="B189" t="s">
+        <v>171</v>
+      </c>
+      <c r="C189" t="s">
+        <v>166</v>
+      </c>
+      <c r="D189" t="s">
+        <v>8</v>
+      </c>
+      <c r="E189" t="s">
+        <v>172</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>78</v>
+      </c>
+      <c r="B190" t="s">
+        <v>171</v>
+      </c>
+      <c r="C190" t="s">
+        <v>166</v>
+      </c>
+      <c r="D190" t="s">
+        <v>8</v>
+      </c>
+      <c r="E190" t="s">
+        <v>173</v>
+      </c>
+      <c r="F190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>78</v>
+      </c>
+      <c r="B191" t="s">
+        <v>171</v>
+      </c>
+      <c r="C191" t="s">
+        <v>166</v>
+      </c>
+      <c r="D191" t="s">
+        <v>8</v>
+      </c>
+      <c r="E191" t="s">
+        <v>174</v>
+      </c>
+      <c r="F191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>78</v>
+      </c>
+      <c r="B192" t="s">
+        <v>171</v>
+      </c>
+      <c r="C192" t="s">
+        <v>166</v>
+      </c>
+      <c r="D192" t="s">
+        <v>8</v>
+      </c>
+      <c r="E192" t="s">
+        <v>175</v>
+      </c>
+      <c r="F192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>78</v>
+      </c>
+      <c r="B193" t="s">
+        <v>171</v>
+      </c>
+      <c r="C193" t="s">
+        <v>166</v>
+      </c>
+      <c r="D193" t="s">
+        <v>8</v>
+      </c>
+      <c r="E193" t="s">
+        <v>176</v>
+      </c>
+      <c r="F193">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>78</v>
+      </c>
+      <c r="B194" t="s">
+        <v>171</v>
+      </c>
+      <c r="C194" t="s">
+        <v>166</v>
+      </c>
+      <c r="D194" t="s">
+        <v>8</v>
+      </c>
+      <c r="E194" t="s">
+        <v>177</v>
+      </c>
+      <c r="F194">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>79</v>
+      </c>
+      <c r="B195" t="s">
+        <v>178</v>
+      </c>
+      <c r="C195" t="s">
+        <v>166</v>
+      </c>
+      <c r="D195" t="s">
+        <v>8</v>
+      </c>
+      <c r="E195" t="s">
         <v>179</v>
       </c>
-      <c r="F179">
-        <v>0.5</v>
+      <c r="F195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>79</v>
+      </c>
+      <c r="B196" t="s">
+        <v>178</v>
+      </c>
+      <c r="C196" t="s">
+        <v>166</v>
+      </c>
+      <c r="D196" t="s">
+        <v>8</v>
+      </c>
+      <c r="E196" t="s">
+        <v>180</v>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>79</v>
+      </c>
+      <c r="B197" t="s">
+        <v>178</v>
+      </c>
+      <c r="C197" t="s">
+        <v>166</v>
+      </c>
+      <c r="D197" t="s">
+        <v>8</v>
+      </c>
+      <c r="E197" t="s">
+        <v>181</v>
+      </c>
+      <c r="F197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>79</v>
+      </c>
+      <c r="B198" t="s">
+        <v>178</v>
+      </c>
+      <c r="C198" t="s">
+        <v>166</v>
+      </c>
+      <c r="D198" t="s">
+        <v>8</v>
+      </c>
+      <c r="E198" t="s">
+        <v>175</v>
+      </c>
+      <c r="F198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>79</v>
+      </c>
+      <c r="B199" t="s">
+        <v>178</v>
+      </c>
+      <c r="C199" t="s">
+        <v>166</v>
+      </c>
+      <c r="D199" t="s">
+        <v>8</v>
+      </c>
+      <c r="E199" t="s">
+        <v>182</v>
+      </c>
+      <c r="F199">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>79</v>
+      </c>
+      <c r="B200" t="s">
+        <v>178</v>
+      </c>
+      <c r="C200" t="s">
+        <v>166</v>
+      </c>
+      <c r="D200" t="s">
+        <v>8</v>
+      </c>
+      <c r="E200" t="s">
+        <v>183</v>
+      </c>
+      <c r="F200">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>79</v>
+      </c>
+      <c r="B201" t="s">
+        <v>178</v>
+      </c>
+      <c r="C201" t="s">
+        <v>166</v>
+      </c>
+      <c r="D201" t="s">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>184</v>
+      </c>
+      <c r="F201">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>80</v>
+      </c>
+      <c r="B202" t="s">
+        <v>185</v>
+      </c>
+      <c r="C202" t="s">
+        <v>166</v>
+      </c>
+      <c r="D202" t="s">
+        <v>8</v>
+      </c>
+      <c r="E202" t="s">
+        <v>167</v>
+      </c>
+      <c r="F202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>80</v>
+      </c>
+      <c r="B203" t="s">
+        <v>185</v>
+      </c>
+      <c r="C203" t="s">
+        <v>166</v>
+      </c>
+      <c r="D203" t="s">
+        <v>8</v>
+      </c>
+      <c r="E203" t="s">
+        <v>170</v>
+      </c>
+      <c r="F203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>13</v>
+      </c>
+      <c r="B204" t="s">
+        <v>221</v>
+      </c>
+      <c r="C204" t="s">
+        <v>7</v>
+      </c>
+      <c r="D204" t="s">
+        <v>222</v>
+      </c>
+      <c r="E204" t="s">
+        <v>223</v>
+      </c>
+      <c r="F204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>13</v>
+      </c>
+      <c r="B205" t="s">
+        <v>221</v>
+      </c>
+      <c r="C205" t="s">
+        <v>7</v>
+      </c>
+      <c r="D205" t="s">
+        <v>222</v>
+      </c>
+      <c r="E205" t="s">
+        <v>224</v>
+      </c>
+      <c r="F205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>13</v>
+      </c>
+      <c r="B206" t="s">
+        <v>221</v>
+      </c>
+      <c r="C206" t="s">
+        <v>7</v>
+      </c>
+      <c r="D206" t="s">
+        <v>222</v>
+      </c>
+      <c r="E206" t="s">
+        <v>225</v>
+      </c>
+      <c r="F206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>14</v>
+      </c>
+      <c r="B207" t="s">
+        <v>226</v>
+      </c>
+      <c r="C207" t="s">
+        <v>7</v>
+      </c>
+      <c r="D207" t="s">
+        <v>222</v>
+      </c>
+      <c r="E207" t="s">
+        <v>227</v>
+      </c>
+      <c r="F207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>14</v>
+      </c>
+      <c r="B208" t="s">
+        <v>226</v>
+      </c>
+      <c r="C208" t="s">
+        <v>7</v>
+      </c>
+      <c r="D208" t="s">
+        <v>222</v>
+      </c>
+      <c r="E208" t="s">
+        <v>228</v>
+      </c>
+      <c r="F208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>14</v>
+      </c>
+      <c r="B209" t="s">
+        <v>226</v>
+      </c>
+      <c r="C209" t="s">
+        <v>7</v>
+      </c>
+      <c r="D209" t="s">
+        <v>222</v>
+      </c>
+      <c r="E209" t="s">
+        <v>229</v>
+      </c>
+      <c r="F209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>16</v>
+      </c>
+      <c r="B210" t="s">
+        <v>230</v>
+      </c>
+      <c r="C210" t="s">
+        <v>7</v>
+      </c>
+      <c r="D210" t="s">
+        <v>222</v>
+      </c>
+      <c r="E210" t="s">
+        <v>231</v>
+      </c>
+      <c r="F210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>16</v>
+      </c>
+      <c r="B211" t="s">
+        <v>230</v>
+      </c>
+      <c r="C211" t="s">
+        <v>7</v>
+      </c>
+      <c r="D211" t="s">
+        <v>222</v>
+      </c>
+      <c r="E211" t="s">
+        <v>232</v>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <v>7</v>
+      </c>
+      <c r="B212" t="s">
+        <v>233</v>
+      </c>
+      <c r="C212" t="s">
+        <v>7</v>
+      </c>
+      <c r="D212" t="s">
+        <v>222</v>
+      </c>
+      <c r="E212" t="s">
+        <v>234</v>
+      </c>
+      <c r="F212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <v>7</v>
+      </c>
+      <c r="B213" t="s">
+        <v>233</v>
+      </c>
+      <c r="C213" t="s">
+        <v>7</v>
+      </c>
+      <c r="D213" t="s">
+        <v>222</v>
+      </c>
+      <c r="E213" t="s">
+        <v>235</v>
+      </c>
+      <c r="F213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>7</v>
+      </c>
+      <c r="B214" t="s">
+        <v>233</v>
+      </c>
+      <c r="C214" t="s">
+        <v>7</v>
+      </c>
+      <c r="D214" t="s">
+        <v>222</v>
+      </c>
+      <c r="E214" t="s">
+        <v>236</v>
+      </c>
+      <c r="F214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>19</v>
+      </c>
+      <c r="B215" t="s">
+        <v>237</v>
+      </c>
+      <c r="C215" t="s">
+        <v>7</v>
+      </c>
+      <c r="D215" t="s">
+        <v>222</v>
+      </c>
+      <c r="E215" t="s">
+        <v>238</v>
+      </c>
+      <c r="F215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>19</v>
+      </c>
+      <c r="B216" t="s">
+        <v>237</v>
+      </c>
+      <c r="C216" t="s">
+        <v>7</v>
+      </c>
+      <c r="D216" t="s">
+        <v>222</v>
+      </c>
+      <c r="E216" t="s">
+        <v>239</v>
+      </c>
+      <c r="F216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <v>19</v>
+      </c>
+      <c r="B217" t="s">
+        <v>237</v>
+      </c>
+      <c r="C217" t="s">
+        <v>7</v>
+      </c>
+      <c r="D217" t="s">
+        <v>222</v>
+      </c>
+      <c r="E217" t="s">
+        <v>240</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <v>8</v>
+      </c>
+      <c r="B218" t="s">
+        <v>241</v>
+      </c>
+      <c r="C218" t="s">
+        <v>7</v>
+      </c>
+      <c r="D218" t="s">
+        <v>222</v>
+      </c>
+      <c r="E218" t="s">
+        <v>242</v>
+      </c>
+      <c r="F218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <v>8</v>
+      </c>
+      <c r="B219" t="s">
+        <v>241</v>
+      </c>
+      <c r="C219" t="s">
+        <v>7</v>
+      </c>
+      <c r="D219" t="s">
+        <v>222</v>
+      </c>
+      <c r="E219" t="s">
+        <v>243</v>
+      </c>
+      <c r="F219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>8</v>
+      </c>
+      <c r="B220" t="s">
+        <v>241</v>
+      </c>
+      <c r="C220" t="s">
+        <v>7</v>
+      </c>
+      <c r="D220" t="s">
+        <v>222</v>
+      </c>
+      <c r="E220" t="s">
+        <v>244</v>
+      </c>
+      <c r="F220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>20</v>
+      </c>
+      <c r="B221" t="s">
+        <v>245</v>
+      </c>
+      <c r="C221" t="s">
+        <v>7</v>
+      </c>
+      <c r="D221" t="s">
+        <v>222</v>
+      </c>
+      <c r="E221" t="s">
+        <v>246</v>
+      </c>
+      <c r="F221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <v>20</v>
+      </c>
+      <c r="B222" t="s">
+        <v>245</v>
+      </c>
+      <c r="C222" t="s">
+        <v>7</v>
+      </c>
+      <c r="D222" t="s">
+        <v>222</v>
+      </c>
+      <c r="E222" t="s">
+        <v>247</v>
+      </c>
+      <c r="F222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <v>20</v>
+      </c>
+      <c r="B223" t="s">
+        <v>245</v>
+      </c>
+      <c r="C223" t="s">
+        <v>7</v>
+      </c>
+      <c r="D223" t="s">
+        <v>222</v>
+      </c>
+      <c r="E223" t="s">
+        <v>248</v>
+      </c>
+      <c r="F223">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
